--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484165_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484165_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1039</v>
+        <v>2.3998</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5013</v>
+        <v>1.9094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6026</v>
+        <v>0.4904</v>
       </c>
       <c r="G2" t="n">
         <v>0.2095</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0975</v>
+        <v>0.1984</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4364</v>
+        <v>-0.0283</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3389</v>
+        <v>0.2267</v>
       </c>
       <c r="V2" t="n">
         <v>0.6032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0352</v>
+        <v>1.7277</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5237</v>
+        <v>1.0759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5115</v>
+        <v>0.6518</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0049</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1276</v>
+        <v>-0.18</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4366</v>
+        <v>-0.0112</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.309</v>
+        <v>-0.1687</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0713</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9386</v>
+        <v>1.2818</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1828</v>
+        <v>1.6087</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2442</v>
+        <v>-0.3269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6833</v>
+        <v>2.3773</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6146</v>
+        <v>1.7282</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0687</v>
+        <v>0.6491</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9488</v>
+        <v>3.6693</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2259</v>
+        <v>2.3791</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7229</v>
+        <v>1.2903</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2654</v>
+        <v>-1.2921</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.6112</v>
+        <v>-0.6509</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6542</v>
+        <v>-0.6412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3887</v>
+        <v>2.9758</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4075</v>
+        <v>0.0595</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.306</v>
+        <v>-0.0055</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1015</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>-2.1469</v>
       </c>
       <c r="W4" t="n">
-        <v>0.532</v>
+        <v>-0.0713</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3891</v>
+        <v>1.1973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9965000000000001</v>
+        <v>3.2452</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6075</v>
+        <v>-2.0478</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3773</v>
+        <v>0.6833</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7282</v>
+        <v>0.6146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6491</v>
+        <v>0.0687</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6693</v>
+        <v>3.9488</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3791</v>
+        <v>3.2259</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2903</v>
+        <v>0.7229</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2921</v>
+        <v>-3.2654</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6509</v>
+        <v>-2.6112</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6412</v>
+        <v>-0.6542</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9758</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.1488</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6177</v>
+        <v>-0.2436</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2155</v>
+        <v>0.0949</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1469</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0713</v>
+        <v>0.532</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0757</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4228</v>
+        <v>-1.7715</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1776</v>
+        <v>-0.8069</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6004</v>
+        <v>-0.9646</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6657</v>
+        <v>-1.8296</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6019</v>
+        <v>-1.1895</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0638</v>
+        <v>-0.64</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5331</v>
+        <v>-0.6199</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0668</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5999</v>
+        <v>-0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1327</v>
+        <v>-1.2097</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6687</v>
+        <v>-1.2097</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4639</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5089</v>
+        <v>-0.1403</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2301</v>
+        <v>-0.187</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2788</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7995</v>
+        <v>-2.447</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8069</v>
+        <v>0.3216</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9926</v>
+        <v>-2.7687</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8296</v>
+        <v>-3.6657</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1895</v>
+        <v>-1.6019</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.64</v>
+        <v>-2.0638</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6199</v>
+        <v>-0.5331</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>0.0668</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.64</v>
+        <v>-0.5999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2097</v>
+        <v>-3.1327</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2097</v>
+        <v>-1.6687</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4639</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1683</v>
+        <v>0.4846</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.187</v>
+        <v>0.3742</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0187</v>
+        <v>0.1105</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8267</v>
+        <v>-3.9134</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8731</v>
+        <v>-2.567</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9536</v>
+        <v>-1.3464</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8519</v>
@@ -1078,13 +1078,13 @@
         <v>2.579</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4976</v>
+        <v>0.411</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.493</v>
+        <v>-0.1869</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9907</v>
+        <v>0.5979</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0757</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.273</v>
+        <v>-4.5651</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5752</v>
+        <v>-4.6149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3022</v>
+        <v>0.0497</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9645</v>
@@ -1156,13 +1156,13 @@
         <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7385</v>
+        <v>0.4464</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3742</v>
+        <v>0.3345</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3643</v>
+        <v>0.1118</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6745</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1213</v>
+        <v>-4.5744</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4069</v>
+        <v>-4.1405</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7144</v>
+        <v>-0.4338</v>
       </c>
       <c r="G10" t="n">
         <v>-6.4436</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8842</v>
+        <v>-0.3372</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5667</v>
+        <v>-0.3003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3175</v>
+        <v>-0.0369</v>
       </c>
       <c r="V10" t="n">
         <v>1.8097</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9765</v>
+        <v>-10.6648</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2802</v>
+        <v>-3.9685</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.6964</v>
+        <v>-6.696299999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-11.4901</v>
@@ -1312,13 +1312,13 @@
         <v>16.8627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4818999999999999</v>
+        <v>0.7935999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5659000000000001</v>
+        <v>-0.2541</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0479</v>
+        <v>1.0481</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9522</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1159</v>
+        <v>3.8872</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2524</v>
+        <v>3.3071</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8635</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4553</v>
+        <v>4.0514</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3063</v>
+        <v>0.9525</v>
       </c>
       <c r="I12" t="n">
-        <v>0.149</v>
+        <v>3.0989</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1654</v>
+        <v>5.3435</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1654</v>
+        <v>1.6034</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.7401</v>
       </c>
       <c r="M12" t="n">
-        <v>0.29</v>
+        <v>-1.2921</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1409</v>
+        <v>-0.6509</v>
       </c>
       <c r="O12" t="n">
-        <v>0.149</v>
+        <v>-0.6412</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>-3.3725</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2086</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.187</v>
+        <v>-0.4023</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0216</v>
+        <v>-0.2424</v>
       </c>
       <c r="V12" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="W12" t="n">
-        <v>0.266</v>
+        <v>1.7384</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.06</v>
+        <v>3.3642</v>
       </c>
       <c r="E13" t="n">
-        <v>3.205</v>
+        <v>2.2524</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1451</v>
+        <v>1.1118</v>
       </c>
       <c r="G13" t="n">
-        <v>4.0514</v>
+        <v>3.4553</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9525</v>
+        <v>3.3063</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0989</v>
+        <v>0.149</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3435</v>
+        <v>3.1654</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6034</v>
+        <v>3.1654</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7401</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2921</v>
+        <v>0.29</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6509</v>
+        <v>0.1409</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6412</v>
+        <v>0.149</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-3.3725</v>
-      </c>
       <c r="R13" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.472</v>
+        <v>0.0396</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5044</v>
+        <v>-0.187</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9676</v>
+        <v>0.2267</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9864</v>
+        <v>3.0679</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7207</v>
+        <v>2.0955</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2657</v>
+        <v>0.9724</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2717</v>
+        <v>0.5758</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6408</v>
+        <v>2.3585</v>
       </c>
       <c r="I14" t="n">
-        <v>0.631</v>
+        <v>-1.7827</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0441</v>
+        <v>2.0088</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9638</v>
+        <v>3.2863</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0803</v>
+        <v>-1.2775</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2277</v>
+        <v>-1.433</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.323</v>
+        <v>-0.9278</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5507</v>
+        <v>-0.5051</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7227</v>
+        <v>-0.1743</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7993</v>
+        <v>-0.6518</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0766</v>
+        <v>0.4774</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2065</v>
+        <v>1.2777</v>
       </c>
       <c r="W14" t="n">
-        <v>0.266</v>
+        <v>1.1352</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4724</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7202</v>
+        <v>2.6165</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6874</v>
+        <v>2.2105</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0328</v>
+        <v>0.406</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5758</v>
+        <v>3.2717</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3585</v>
+        <v>2.6408</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7827</v>
+        <v>0.631</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0088</v>
+        <v>3.0441</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2863</v>
+        <v>2.9638</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2775</v>
+        <v>0.0803</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.433</v>
+        <v>0.2277</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9278</v>
+        <v>-0.323</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5051</v>
+        <v>0.5507</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5221</v>
+        <v>0.3528</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0599</v>
+        <v>0.2891</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2777</v>
+        <v>-1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1352</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1425</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5228</v>
+        <v>1.771</v>
       </c>
       <c r="E16" t="n">
         <v>1.6312</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1084</v>
+        <v>0.1399</v>
       </c>
       <c r="G16" t="n">
         <v>1.5151</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0635</v>
+        <v>0.3117</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1303</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1938</v>
+        <v>0.442</v>
       </c>
       <c r="V16" t="n">
         <v>0.1425</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3971</v>
+        <v>0.9941</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3741</v>
+        <v>-1.2721</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7711</v>
+        <v>2.2661</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1014</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.1388</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3173</v>
+        <v>-0.2153</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8591</v>
+        <v>0.3541</v>
       </c>
       <c r="V17" t="n">
         <v>3.3534</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8182</v>
+        <v>0.4395</v>
       </c>
       <c r="E18" t="n">
-        <v>1.37</v>
+        <v>-1.5094</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5518</v>
+        <v>1.9489</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0392</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4368</v>
+        <v>-0.3075</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6024</v>
+        <v>-0.4107</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0392</v>
+        <v>-1.0786</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4368</v>
+        <v>-0.5189</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6024</v>
+        <v>-0.5597</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.3604</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.2114</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.9758</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-0.1984</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6952</v>
+        <v>0.1658</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0406</v>
+        <v>-0.2324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6546</v>
+        <v>0.3981</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,75 +1891,71 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2074</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7134</v>
+        <v>-0.2516</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9208</v>
+        <v>0.3381</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7181999999999999</v>
+        <v>0.1678</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3075</v>
+        <v>0.2572</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4107</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0786</v>
+        <v>-0.2517</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5189</v>
+        <v>-0.2918</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5597</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3604</v>
+        <v>0.4195</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2114</v>
+        <v>0.549</v>
       </c>
       <c r="O19" t="n">
-        <v>0.149</v>
+        <v>-0.1295</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0663</v>
+        <v>0.3316</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4364</v>
+        <v>0.1984</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3701</v>
+        <v>0.1332</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P. MULIO CAMPOS</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1969,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4798</v>
+        <v>-0.633</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7618</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.282</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1678</v>
+        <v>-1.4464</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2572</v>
+        <v>-0.6808</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2517</v>
+        <v>0.3421</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2918</v>
+        <v>0.1815</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>0.1606</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4195</v>
+        <v>-1.7885</v>
       </c>
       <c r="N20" t="n">
-        <v>0.549</v>
+        <v>-0.8623</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1295</v>
+        <v>-0.9263</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1984</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2347</v>
+        <v>-0.5753</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3117</v>
+        <v>-0.238</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0771</v>
+        <v>-0.3373</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,71 +2043,75 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8535</v>
+        <v>-0.633</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3715</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.482</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7581</v>
+        <v>-1.4464</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.6808</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6827</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6827</v>
+        <v>0.3421</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1815</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6827</v>
+        <v>0.1606</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07530000000000001</v>
+        <v>-1.7885</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.8623</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.9263</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2148</v>
+        <v>-0.5753</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0623</v>
+        <v>-0.238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1525</v>
+        <v>-0.3373</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>,. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4476</v>
+        <v>-0.6867</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6044</v>
+        <v>0.1456</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8431</v>
+        <v>-0.8324</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4464</v>
+        <v>2.0392</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6808</v>
+        <v>1.4368</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.6024</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3421</v>
+        <v>2.0392</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1815</v>
+        <v>1.4368</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1606</v>
+        <v>0.6024</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7885</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8623</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9263</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3887</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1984</v>
+        <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3898</v>
+        <v>1.1903</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7481</v>
+        <v>0.8162</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6417</v>
+        <v>0.3741</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4476</v>
+        <v>-0.9377</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6044</v>
+        <v>-0.3715</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8431</v>
+        <v>-0.5662</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4464</v>
+        <v>0.7581</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6808</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.6827</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3421</v>
+        <v>0.6827</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1815</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1606</v>
+        <v>0.6827</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7885</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8623</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9263</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3887</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3898</v>
+        <v>-0.299</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7481</v>
+        <v>-0.0623</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6417</v>
+        <v>-0.2367</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="24">
@@ -2277,10 +2277,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0705</v>
+        <v>-1.8664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3451</v>
+        <v>-1.141</v>
       </c>
       <c r="F24" t="n">
         <v>-0.7254</v>
@@ -2322,10 +2322,10 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3968</v>
+        <v>-0.1927</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1303</v>
+        <v>0.0738</v>
       </c>
       <c r="U24" t="n">
         <v>-0.2665</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.529</v>
+        <v>11.4701</v>
       </c>
       <c r="E25" t="n">
-        <v>6.092000000000002</v>
+        <v>6.908100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.437000000000001</v>
+        <v>4.561699999999998</v>
       </c>
       <c r="G25" t="n">
         <v>10.0434</v>
@@ -2391,7 +2391,7 @@
         <v>-4.099699999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5952</v>
+        <v>-0.5951999999999996</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.0611</v>
@@ -2400,13 +2400,13 @@
         <v>16.466</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8717</v>
+        <v>0.06929999999999972</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7959</v>
+        <v>-0.9798999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07570000000000038</v>
+        <v>1.0491</v>
       </c>
       <c r="V25" t="n">
         <v>1.9521</v>
